--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,26 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salariunioni2.DECABO\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F589A1F2-C491-4843-AFEC-23672898A083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="1330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1355">
   <si>
     <t>Codice</t>
   </si>
@@ -505,7 +497,7 @@
     <t>bol5093</t>
   </si>
   <si>
-    <t>BOLZANO 24</t>
+    <t>BOLZANO 24(PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Bolzano, 24</t>
@@ -1285,7 +1277,7 @@
     <t>Fop9017</t>
   </si>
   <si>
-    <t>FOPPA 39 - PERSA DALLA 23/24</t>
+    <t>FOPPA 39 - SOLO LETTURE</t>
   </si>
   <si>
     <t>Via Foppa Vincenzo, 39</t>
@@ -2146,7 +2138,7 @@
     <t>PAD5777</t>
   </si>
   <si>
-    <t>PADOVA,27</t>
+    <t>PADOVA 27</t>
   </si>
   <si>
     <t>Via Padova, 27</t>
@@ -2758,7 +2750,7 @@
     <t>DEL5738</t>
   </si>
   <si>
-    <t>SEBASTIANO DEL PIOMBO 11 DEL PIOMBO 11</t>
+    <t>SEBASTIANO DEL PIOMBO 11( PERSA 25-26) DEL PIOMBO 11</t>
   </si>
   <si>
     <t>Via Sebastiano Del Piombo, 11</t>
@@ -3292,6 +3284,18 @@
     <t>95594900151</t>
   </si>
   <si>
+    <t>FER6362</t>
+  </si>
+  <si>
+    <t>FERRUCCI 14</t>
+  </si>
+  <si>
+    <t>Via Francesco Ferrucci, 14</t>
+  </si>
+  <si>
+    <t>80179300159</t>
+  </si>
+  <si>
     <t>SAN4974</t>
   </si>
   <si>
@@ -3445,7 +3449,7 @@
     <t>RAV8870</t>
   </si>
   <si>
-    <t>RAVIZZA 36</t>
+    <t>RAVIZZA 36( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Ravizza Carlo, 36</t>
@@ -3715,7 +3719,7 @@
     <t>MAGENTA 121 - CONDOMINIO NETTUNO</t>
   </si>
   <si>
-    <t>Via magenta, 121</t>
+    <t>Via Gorizia, 121</t>
   </si>
   <si>
     <t>85033870156</t>
@@ -3808,7 +3812,7 @@
     <t>CAR8394</t>
   </si>
   <si>
-    <t>CAPRI 11A</t>
+    <t>CAPRI 11A( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Capri, 11</t>
@@ -3877,7 +3881,7 @@
     <t>CAP1540</t>
   </si>
   <si>
-    <t>CAPRI 11B</t>
+    <t>CAPRI 11B( PERSA 25-26)</t>
   </si>
   <si>
     <t>TIZ3573</t>
@@ -3943,6 +3947,18 @@
     <t>95582840153</t>
   </si>
   <si>
+    <t>GEN4700</t>
+  </si>
+  <si>
+    <t>GENOVA 27</t>
+  </si>
+  <si>
+    <t>Corso genova, 27</t>
+  </si>
+  <si>
+    <t>97387530153</t>
+  </si>
+  <si>
     <t>LIS7337</t>
   </si>
   <si>
@@ -4010,13 +4026,64 @@
   </si>
   <si>
     <t>CHNDLA37T54F205A</t>
+  </si>
+  <si>
+    <t>MOL1254</t>
+  </si>
+  <si>
+    <t>MOLINO TUONO 90</t>
+  </si>
+  <si>
+    <t>Via Molino Tuono, 90 S.2</t>
+  </si>
+  <si>
+    <t>GIA6091</t>
+  </si>
+  <si>
+    <t>GIAN BATTISTA VICO 4</t>
+  </si>
+  <si>
+    <t>Via Vico Gian Battista, 4 S.1</t>
+  </si>
+  <si>
+    <t>03381150154</t>
+  </si>
+  <si>
+    <t>TAR4097</t>
+  </si>
+  <si>
+    <t>TARTINI 28</t>
+  </si>
+  <si>
+    <t>Via Tartini Giuseppe, 28 S.1</t>
+  </si>
+  <si>
+    <t>95599760154</t>
+  </si>
+  <si>
+    <t>SIG4442</t>
+  </si>
+  <si>
+    <t>SIGNORELLI 4</t>
+  </si>
+  <si>
+    <t>Via Signorelli Luca, 4</t>
+  </si>
+  <si>
+    <t>DET2995</t>
+  </si>
+  <si>
+    <t>DE TOGNI 23</t>
+  </si>
+  <si>
+    <t>Via De Togni Aristide, 23</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -4064,7 +4131,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4079,7 +4145,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4094,7 +4159,6 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -4103,7 +4167,7 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -4117,18 +4181,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -4418,24 +4474,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D7F4A9-30E7-BF0D-ED09-8DB5C1C71512}">
-  <dimension ref="A1:L309"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{40FEE0AB-6D11-C1BE-B96A-19EA3A7E9B16}" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:CV321"/>
+  <sheetFormatPr defaultColWidth="8.8515625" customHeight="1" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" customWidth="1"/>
-    <col min="2" max="2" width="71" customWidth="1"/>
-    <col min="3" max="3" width="33.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" customWidth="1"/>
-    <col min="6" max="6" width="5.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="9.26953125" customWidth="1"/>
-    <col min="9" max="10" width="19.54296875" customWidth="1"/>
-    <col min="11" max="11" width="62.26953125" customWidth="1"/>
-    <col min="12" max="12" width="60.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.28125" customWidth="1"/>
+    <col min="2" max="2" width="71.00390625" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.8515625" customWidth="1"/>
+    <col min="5" max="5" width="8.28125" customWidth="1"/>
+    <col min="6" max="6" width="5.8515625" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.28125" customWidth="1"/>
+    <col min="9" max="10" width="19.57421875" customWidth="1"/>
+    <col min="11" max="11" width="62.28125" customWidth="1"/>
+    <col min="12" max="12" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4473,7 +4529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -4511,7 +4567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -4549,7 +4605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -4587,7 +4643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A5" s="3" t="s">
         <v>33</v>
       </c>
@@ -4625,7 +4681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -4663,7 +4719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -4701,7 +4757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -4739,7 +4795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A9" s="3" t="s">
         <v>54</v>
       </c>
@@ -4777,7 +4833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
@@ -4815,7 +4871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
@@ -4853,7 +4909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -4891,7 +4947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
@@ -4929,7 +4985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -4967,7 +5023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A15" s="3" t="s">
         <v>84</v>
       </c>
@@ -5005,7 +5061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -5043,7 +5099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -5081,7 +5137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A18" s="2" t="s">
         <v>99</v>
       </c>
@@ -5117,7 +5173,7 @@
       </c>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A19" s="3" t="s">
         <v>104</v>
       </c>
@@ -5155,7 +5211,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A20" s="2" t="s">
         <v>110</v>
       </c>
@@ -5193,7 +5249,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A21" s="3" t="s">
         <v>114</v>
       </c>
@@ -5231,7 +5287,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A22" s="2" t="s">
         <v>118</v>
       </c>
@@ -5269,7 +5325,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A23" s="3" t="s">
         <v>122</v>
       </c>
@@ -5307,7 +5363,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A24" s="2" t="s">
         <v>126</v>
       </c>
@@ -5345,7 +5401,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A25" s="3" t="s">
         <v>131</v>
       </c>
@@ -5383,7 +5439,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A26" s="2" t="s">
         <v>136</v>
       </c>
@@ -5421,7 +5477,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A27" s="3" t="s">
         <v>141</v>
       </c>
@@ -5459,7 +5515,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A28" s="2" t="s">
         <v>146</v>
       </c>
@@ -5497,7 +5553,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A29" s="3" t="s">
         <v>150</v>
       </c>
@@ -5535,7 +5591,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A30" s="2" t="s">
         <v>156</v>
       </c>
@@ -5573,7 +5629,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A31" s="3" t="s">
         <v>160</v>
       </c>
@@ -5611,7 +5667,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A32" s="2" t="s">
         <v>164</v>
       </c>
@@ -5649,7 +5705,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A33" s="3" t="s">
         <v>168</v>
       </c>
@@ -5687,7 +5743,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A34" s="2" t="s">
         <v>172</v>
       </c>
@@ -5725,7 +5781,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A35" s="3" t="s">
         <v>176</v>
       </c>
@@ -5763,7 +5819,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A36" s="2" t="s">
         <v>181</v>
       </c>
@@ -5801,7 +5857,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A37" s="3" t="s">
         <v>185</v>
       </c>
@@ -5839,7 +5895,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A38" s="2" t="s">
         <v>192</v>
       </c>
@@ -5877,7 +5933,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A39" s="3" t="s">
         <v>197</v>
       </c>
@@ -5915,7 +5971,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A40" s="2" t="s">
         <v>201</v>
       </c>
@@ -5953,7 +6009,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A41" s="3" t="s">
         <v>206</v>
       </c>
@@ -5991,7 +6047,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A42" s="2" t="s">
         <v>210</v>
       </c>
@@ -6029,7 +6085,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A43" s="3" t="s">
         <v>215</v>
       </c>
@@ -6067,7 +6123,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A44" s="2" t="s">
         <v>219</v>
       </c>
@@ -6105,7 +6161,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A45" s="3" t="s">
         <v>223</v>
       </c>
@@ -6143,7 +6199,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A46" s="2" t="s">
         <v>227</v>
       </c>
@@ -6181,7 +6237,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A47" s="3" t="s">
         <v>231</v>
       </c>
@@ -6219,7 +6275,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A48" s="2" t="s">
         <v>235</v>
       </c>
@@ -6257,7 +6313,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A49" s="3" t="s">
         <v>238</v>
       </c>
@@ -6295,7 +6351,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A50" s="2" t="s">
         <v>242</v>
       </c>
@@ -6333,7 +6389,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A51" s="3" t="s">
         <v>247</v>
       </c>
@@ -6371,7 +6427,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A52" s="2" t="s">
         <v>251</v>
       </c>
@@ -6409,7 +6465,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A53" s="3" t="s">
         <v>255</v>
       </c>
@@ -6447,7 +6503,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A54" s="2" t="s">
         <v>259</v>
       </c>
@@ -6485,7 +6541,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A55" s="3" t="s">
         <v>264</v>
       </c>
@@ -6523,7 +6579,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A56" s="2" t="s">
         <v>268</v>
       </c>
@@ -6561,7 +6617,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A57" s="3" t="s">
         <v>273</v>
       </c>
@@ -6599,7 +6655,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A58" s="2" t="s">
         <v>277</v>
       </c>
@@ -6637,7 +6693,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A59" s="3" t="s">
         <v>282</v>
       </c>
@@ -6675,7 +6731,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A60" s="2" t="s">
         <v>286</v>
       </c>
@@ -6713,7 +6769,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A61" s="3" t="s">
         <v>290</v>
       </c>
@@ -6751,7 +6807,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A62" s="2" t="s">
         <v>294</v>
       </c>
@@ -6789,7 +6845,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A63" s="3" t="s">
         <v>298</v>
       </c>
@@ -6827,7 +6883,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A64" s="2" t="s">
         <v>303</v>
       </c>
@@ -6865,7 +6921,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A65" s="3" t="s">
         <v>308</v>
       </c>
@@ -6903,7 +6959,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A66" s="2" t="s">
         <v>312</v>
       </c>
@@ -6941,7 +6997,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A67" s="3" t="s">
         <v>316</v>
       </c>
@@ -6979,7 +7035,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A68" s="2" t="s">
         <v>322</v>
       </c>
@@ -7017,7 +7073,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A69" s="3" t="s">
         <v>328</v>
       </c>
@@ -7055,7 +7111,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A70" s="2" t="s">
         <v>332</v>
       </c>
@@ -7093,7 +7149,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A71" s="3" t="s">
         <v>336</v>
       </c>
@@ -7131,7 +7187,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A72" s="2" t="s">
         <v>341</v>
       </c>
@@ -7169,7 +7225,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A73" s="3" t="s">
         <v>346</v>
       </c>
@@ -7207,7 +7263,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A74" s="2" t="s">
         <v>351</v>
       </c>
@@ -7245,7 +7301,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A75" s="3" t="s">
         <v>355</v>
       </c>
@@ -7283,7 +7339,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A76" s="2" t="s">
         <v>360</v>
       </c>
@@ -7321,7 +7377,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A77" s="3" t="s">
         <v>364</v>
       </c>
@@ -7359,7 +7415,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A78" s="2" t="s">
         <v>369</v>
       </c>
@@ -7397,7 +7453,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A79" s="3" t="s">
         <v>373</v>
       </c>
@@ -7435,7 +7491,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A80" s="2" t="s">
         <v>377</v>
       </c>
@@ -7473,7 +7529,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A81" s="3" t="s">
         <v>381</v>
       </c>
@@ -7511,7 +7567,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A82" s="2" t="s">
         <v>384</v>
       </c>
@@ -7549,7 +7605,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A83" s="3" t="s">
         <v>388</v>
       </c>
@@ -7587,7 +7643,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A84" s="2" t="s">
         <v>392</v>
       </c>
@@ -7625,7 +7681,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A85" s="3" t="s">
         <v>397</v>
       </c>
@@ -7663,7 +7719,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A86" s="2" t="s">
         <v>401</v>
       </c>
@@ -7701,7 +7757,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A87" s="3" t="s">
         <v>407</v>
       </c>
@@ -7739,7 +7795,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A88" s="2" t="s">
         <v>411</v>
       </c>
@@ -7777,7 +7833,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A89" s="3" t="s">
         <v>415</v>
       </c>
@@ -7815,7 +7871,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A90" s="2" t="s">
         <v>420</v>
       </c>
@@ -7851,7 +7907,7 @@
       </c>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A91" s="3" t="s">
         <v>424</v>
       </c>
@@ -7889,7 +7945,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A92" s="2" t="s">
         <v>428</v>
       </c>
@@ -7927,7 +7983,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A93" s="3" t="s">
         <v>432</v>
       </c>
@@ -7965,7 +8021,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A94" s="2" t="s">
         <v>436</v>
       </c>
@@ -8003,7 +8059,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A95" s="3" t="s">
         <v>441</v>
       </c>
@@ -8041,7 +8097,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A96" s="2" t="s">
         <v>445</v>
       </c>
@@ -8079,7 +8135,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A97" s="3" t="s">
         <v>450</v>
       </c>
@@ -8117,7 +8173,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A98" s="2" t="s">
         <v>454</v>
       </c>
@@ -8155,7 +8211,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A99" s="3" t="s">
         <v>458</v>
       </c>
@@ -8193,7 +8249,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A100" s="2" t="s">
         <v>463</v>
       </c>
@@ -8231,7 +8287,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A101" s="3" t="s">
         <v>467</v>
       </c>
@@ -8269,7 +8325,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A102" s="2" t="s">
         <v>472</v>
       </c>
@@ -8307,7 +8363,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A103" s="3" t="s">
         <v>476</v>
       </c>
@@ -8345,7 +8401,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A104" s="2" t="s">
         <v>479</v>
       </c>
@@ -8383,7 +8439,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A105" s="3" t="s">
         <v>483</v>
       </c>
@@ -8421,7 +8477,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A106" s="2" t="s">
         <v>487</v>
       </c>
@@ -8459,7 +8515,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A107" s="3" t="s">
         <v>491</v>
       </c>
@@ -8497,7 +8553,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A108" s="2" t="s">
         <v>495</v>
       </c>
@@ -8535,7 +8591,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A109" s="3" t="s">
         <v>500</v>
       </c>
@@ -8573,7 +8629,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A110" s="2" t="s">
         <v>504</v>
       </c>
@@ -8611,7 +8667,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A111" s="3" t="s">
         <v>508</v>
       </c>
@@ -8649,7 +8705,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A112" s="2" t="s">
         <v>513</v>
       </c>
@@ -8687,7 +8743,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A113" s="3" t="s">
         <v>516</v>
       </c>
@@ -8725,7 +8781,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A114" s="2" t="s">
         <v>520</v>
       </c>
@@ -8763,7 +8819,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A115" s="3" t="s">
         <v>524</v>
       </c>
@@ -8801,7 +8857,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A116" s="2" t="s">
         <v>528</v>
       </c>
@@ -8839,7 +8895,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A117" s="3" t="s">
         <v>532</v>
       </c>
@@ -8877,7 +8933,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A118" s="2" t="s">
         <v>536</v>
       </c>
@@ -8915,7 +8971,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A119" s="3" t="s">
         <v>540</v>
       </c>
@@ -8953,7 +9009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A120" s="2" t="s">
         <v>544</v>
       </c>
@@ -8991,7 +9047,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A121" s="3" t="s">
         <v>549</v>
       </c>
@@ -9029,7 +9085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A122" s="2" t="s">
         <v>553</v>
       </c>
@@ -9067,7 +9123,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A123" s="3" t="s">
         <v>559</v>
       </c>
@@ -9105,7 +9161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A124" s="2" t="s">
         <v>563</v>
       </c>
@@ -9143,7 +9199,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A125" s="3" t="s">
         <v>567</v>
       </c>
@@ -9181,7 +9237,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A126" s="2" t="s">
         <v>571</v>
       </c>
@@ -9219,7 +9275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A127" s="3" t="s">
         <v>576</v>
       </c>
@@ -9257,7 +9313,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A128" s="2" t="s">
         <v>580</v>
       </c>
@@ -9295,7 +9351,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A129" s="3" t="s">
         <v>584</v>
       </c>
@@ -9333,7 +9389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A130" s="2" t="s">
         <v>590</v>
       </c>
@@ -9371,7 +9427,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A131" s="3" t="s">
         <v>594</v>
       </c>
@@ -9409,7 +9465,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A132" s="2" t="s">
         <v>598</v>
       </c>
@@ -9447,7 +9503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A133" s="3" t="s">
         <v>602</v>
       </c>
@@ -9485,7 +9541,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A134" s="2" t="s">
         <v>605</v>
       </c>
@@ -9523,7 +9579,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A135" s="3" t="s">
         <v>609</v>
       </c>
@@ -9561,7 +9617,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A136" s="2" t="s">
         <v>613</v>
       </c>
@@ -9599,7 +9655,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A137" s="3" t="s">
         <v>617</v>
       </c>
@@ -9637,7 +9693,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A138" s="2" t="s">
         <v>621</v>
       </c>
@@ -9675,7 +9731,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A139" s="3" t="s">
         <v>625</v>
       </c>
@@ -9713,7 +9769,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A140" s="2" t="s">
         <v>629</v>
       </c>
@@ -9751,7 +9807,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A141" s="3" t="s">
         <v>634</v>
       </c>
@@ -9789,7 +9845,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A142" s="2" t="s">
         <v>638</v>
       </c>
@@ -9827,7 +9883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A143" s="3" t="s">
         <v>642</v>
       </c>
@@ -9865,7 +9921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A144" s="2" t="s">
         <v>645</v>
       </c>
@@ -9903,7 +9959,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A145" s="3" t="s">
         <v>649</v>
       </c>
@@ -9941,7 +9997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A146" s="2" t="s">
         <v>653</v>
       </c>
@@ -9979,7 +10035,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A147" s="3" t="s">
         <v>657</v>
       </c>
@@ -10017,7 +10073,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A148" s="2" t="s">
         <v>661</v>
       </c>
@@ -10055,7 +10111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A149" s="3" t="s">
         <v>666</v>
       </c>
@@ -10093,7 +10149,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A150" s="2" t="s">
         <v>670</v>
       </c>
@@ -10131,7 +10187,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A151" s="3" t="s">
         <v>674</v>
       </c>
@@ -10169,7 +10225,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A152" s="2" t="s">
         <v>678</v>
       </c>
@@ -10207,7 +10263,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A153" s="3" t="s">
         <v>682</v>
       </c>
@@ -10245,7 +10301,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A154" s="2" t="s">
         <v>686</v>
       </c>
@@ -10283,7 +10339,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A155" s="3" t="s">
         <v>690</v>
       </c>
@@ -10321,7 +10377,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A156" s="2" t="s">
         <v>694</v>
       </c>
@@ -10359,7 +10415,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A157" s="3" t="s">
         <v>699</v>
       </c>
@@ -10397,7 +10453,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A158" s="2" t="s">
         <v>703</v>
       </c>
@@ -10435,7 +10491,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A159" s="3" t="s">
         <v>707</v>
       </c>
@@ -10473,7 +10529,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A160" s="2" t="s">
         <v>711</v>
       </c>
@@ -10511,7 +10567,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A161" s="3" t="s">
         <v>717</v>
       </c>
@@ -10549,7 +10605,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A162" s="2" t="s">
         <v>721</v>
       </c>
@@ -10587,7 +10643,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A163" s="3" t="s">
         <v>725</v>
       </c>
@@ -10625,7 +10681,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A164" s="2" t="s">
         <v>729</v>
       </c>
@@ -10663,7 +10719,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A165" s="3" t="s">
         <v>733</v>
       </c>
@@ -10701,7 +10757,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A166" s="2" t="s">
         <v>737</v>
       </c>
@@ -10739,7 +10795,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A167" s="3" t="s">
         <v>744</v>
       </c>
@@ -10777,7 +10833,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A168" s="2" t="s">
         <v>750</v>
       </c>
@@ -10815,7 +10871,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A169" s="3" t="s">
         <v>754</v>
       </c>
@@ -10853,7 +10909,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A170" s="2" t="s">
         <v>758</v>
       </c>
@@ -10891,7 +10947,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A171" s="3" t="s">
         <v>761</v>
       </c>
@@ -10929,7 +10985,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A172" s="2" t="s">
         <v>765</v>
       </c>
@@ -10967,7 +11023,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A173" s="3" t="s">
         <v>769</v>
       </c>
@@ -11005,7 +11061,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A174" s="2" t="s">
         <v>773</v>
       </c>
@@ -11043,7 +11099,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A175" s="3" t="s">
         <v>777</v>
       </c>
@@ -11081,7 +11137,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A176" s="2" t="s">
         <v>781</v>
       </c>
@@ -11119,7 +11175,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A177" s="3" t="s">
         <v>785</v>
       </c>
@@ -11157,7 +11213,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A178" s="2" t="s">
         <v>789</v>
       </c>
@@ -11195,7 +11251,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A179" s="3" t="s">
         <v>793</v>
       </c>
@@ -11233,7 +11289,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A180" s="2" t="s">
         <v>797</v>
       </c>
@@ -11271,7 +11327,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A181" s="3" t="s">
         <v>801</v>
       </c>
@@ -11309,7 +11365,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A182" s="2" t="s">
         <v>805</v>
       </c>
@@ -11347,7 +11403,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A183" s="3" t="s">
         <v>809</v>
       </c>
@@ -11385,7 +11441,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A184" s="2" t="s">
         <v>813</v>
       </c>
@@ -11423,7 +11479,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A185" s="3" t="s">
         <v>818</v>
       </c>
@@ -11461,7 +11517,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A186" s="2" t="s">
         <v>822</v>
       </c>
@@ -11499,7 +11555,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A187" s="3" t="s">
         <v>826</v>
       </c>
@@ -11537,7 +11593,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A188" s="2" t="s">
         <v>830</v>
       </c>
@@ -11575,7 +11631,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A189" s="3" t="s">
         <v>834</v>
       </c>
@@ -11613,7 +11669,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A190" s="2" t="s">
         <v>838</v>
       </c>
@@ -11651,7 +11707,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A191" s="3" t="s">
         <v>844</v>
       </c>
@@ -11689,7 +11745,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A192" s="2" t="s">
         <v>848</v>
       </c>
@@ -11727,7 +11783,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A193" s="3" t="s">
         <v>852</v>
       </c>
@@ -11765,7 +11821,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A194" s="2" t="s">
         <v>857</v>
       </c>
@@ -11803,7 +11859,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A195" s="3" t="s">
         <v>861</v>
       </c>
@@ -11841,7 +11897,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A196" s="2" t="s">
         <v>865</v>
       </c>
@@ -11879,7 +11935,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A197" s="3" t="s">
         <v>870</v>
       </c>
@@ -11917,7 +11973,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A198" s="2" t="s">
         <v>874</v>
       </c>
@@ -11955,7 +12011,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A199" s="3" t="s">
         <v>878</v>
       </c>
@@ -11993,7 +12049,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A200" s="2" t="s">
         <v>882</v>
       </c>
@@ -12031,7 +12087,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A201" s="3" t="s">
         <v>886</v>
       </c>
@@ -12069,7 +12125,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A202" s="2" t="s">
         <v>890</v>
       </c>
@@ -12107,7 +12163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A203" s="3" t="s">
         <v>894</v>
       </c>
@@ -12145,7 +12201,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A204" s="2" t="s">
         <v>898</v>
       </c>
@@ -12183,7 +12239,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A205" s="3" t="s">
         <v>903</v>
       </c>
@@ -12221,7 +12277,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A206" s="2" t="s">
         <v>907</v>
       </c>
@@ -12259,7 +12315,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A207" s="3" t="s">
         <v>911</v>
       </c>
@@ -12297,7 +12353,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A208" s="2" t="s">
         <v>915</v>
       </c>
@@ -12335,7 +12391,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A209" s="3" t="s">
         <v>919</v>
       </c>
@@ -12373,7 +12429,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A210" s="2" t="s">
         <v>923</v>
       </c>
@@ -12411,7 +12467,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A211" s="3" t="s">
         <v>927</v>
       </c>
@@ -12449,7 +12505,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A212" s="2" t="s">
         <v>931</v>
       </c>
@@ -12487,7 +12543,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A213" s="3" t="s">
         <v>935</v>
       </c>
@@ -12525,7 +12581,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A214" s="2" t="s">
         <v>939</v>
       </c>
@@ -12563,7 +12619,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A215" s="3" t="s">
         <v>943</v>
       </c>
@@ -12601,7 +12657,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A216" s="2" t="s">
         <v>947</v>
       </c>
@@ -12639,7 +12695,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A217" s="3" t="s">
         <v>952</v>
       </c>
@@ -12677,7 +12733,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A218" s="2" t="s">
         <v>956</v>
       </c>
@@ -12715,7 +12771,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A219" s="3" t="s">
         <v>960</v>
       </c>
@@ -12753,7 +12809,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A220" s="2" t="s">
         <v>964</v>
       </c>
@@ -12791,7 +12847,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A221" s="3" t="s">
         <v>968</v>
       </c>
@@ -12829,7 +12885,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A222" s="2" t="s">
         <v>972</v>
       </c>
@@ -12867,7 +12923,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A223" s="3" t="s">
         <v>976</v>
       </c>
@@ -12905,7 +12961,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A224" s="2" t="s">
         <v>980</v>
       </c>
@@ -12943,7 +12999,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A225" s="3" t="s">
         <v>984</v>
       </c>
@@ -12981,7 +13037,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A226" s="2" t="s">
         <v>988</v>
       </c>
@@ -13019,7 +13075,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A227" s="3" t="s">
         <v>992</v>
       </c>
@@ -13057,7 +13113,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A228" s="2" t="s">
         <v>996</v>
       </c>
@@ -13095,7 +13151,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A229" s="3" t="s">
         <v>1000</v>
       </c>
@@ -13133,7 +13189,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A230" s="2" t="s">
         <v>1004</v>
       </c>
@@ -13171,7 +13227,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A231" s="3" t="s">
         <v>1008</v>
       </c>
@@ -13209,7 +13265,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A232" s="2" t="s">
         <v>1012</v>
       </c>
@@ -13247,7 +13303,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A233" s="3" t="s">
         <v>1016</v>
       </c>
@@ -13283,7 +13339,7 @@
       </c>
       <c r="L233" s="3"/>
     </row>
-    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A234" s="2" t="s">
         <v>1019</v>
       </c>
@@ -13319,7 +13375,7 @@
       </c>
       <c r="L234" s="2"/>
     </row>
-    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A235" s="3" t="s">
         <v>1023</v>
       </c>
@@ -13357,7 +13413,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A236" s="2" t="s">
         <v>1027</v>
       </c>
@@ -13395,7 +13451,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A237" s="3" t="s">
         <v>1031</v>
       </c>
@@ -13433,7 +13489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A238" s="2" t="s">
         <v>1037</v>
       </c>
@@ -13471,7 +13527,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A239" s="3" t="s">
         <v>1041</v>
       </c>
@@ -13509,7 +13565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A240" s="2" t="s">
         <v>1045</v>
       </c>
@@ -13547,7 +13603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A241" s="3" t="s">
         <v>1049</v>
       </c>
@@ -13585,7 +13641,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A242" s="2" t="s">
         <v>1053</v>
       </c>
@@ -13623,7 +13679,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A243" s="3" t="s">
         <v>1057</v>
       </c>
@@ -13661,7 +13717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A244" s="2" t="s">
         <v>1061</v>
       </c>
@@ -13699,7 +13755,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A245" s="3" t="s">
         <v>1065</v>
       </c>
@@ -13737,7 +13793,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A246" s="2" t="s">
         <v>1069</v>
       </c>
@@ -13775,7 +13831,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A247" s="3" t="s">
         <v>1073</v>
       </c>
@@ -13813,7 +13869,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A248" s="2" t="s">
         <v>1077</v>
       </c>
@@ -13851,7 +13907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A249" s="3" t="s">
         <v>1083</v>
       </c>
@@ -13889,7 +13945,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A250" s="2" t="s">
         <v>1086</v>
       </c>
@@ -13927,7 +13983,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A251" s="3" t="s">
         <v>1090</v>
       </c>
@@ -13944,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>18</v>
@@ -13962,10 +14018,10 @@
         <v>20</v>
       </c>
       <c r="L251" s="3" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A252" s="2" t="s">
         <v>1094</v>
       </c>
@@ -13982,7 +14038,7 @@
         <v>16</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>213</v>
+        <v>92</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>18</v>
@@ -14003,7 +14059,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A253" s="3" t="s">
         <v>1098</v>
       </c>
@@ -14020,7 +14076,7 @@
         <v>16</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="G253" s="3" t="s">
         <v>18</v>
@@ -14038,10 +14094,10 @@
         <v>20</v>
       </c>
       <c r="L253" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>856</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A254" s="2" t="s">
         <v>1102</v>
       </c>
@@ -14058,7 +14114,7 @@
         <v>16</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>18</v>
@@ -14079,7 +14135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A255" s="3" t="s">
         <v>1106</v>
       </c>
@@ -14096,7 +14152,7 @@
         <v>16</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>18</v>
@@ -14114,10 +14170,10 @@
         <v>20</v>
       </c>
       <c r="L255" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A256" s="2" t="s">
         <v>1110</v>
       </c>
@@ -14128,13 +14184,13 @@
         <v>1112</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>1034</v>
+        <v>15</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1035</v>
+        <v>62</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>18</v>
@@ -14152,10 +14208,10 @@
         <v>20</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A257" s="3" t="s">
         <v>1114</v>
       </c>
@@ -14166,63 +14222,63 @@
         <v>1116</v>
       </c>
       <c r="D257" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J257" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K257" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L257" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A258" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D258" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="E257" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G257" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H257" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I257" s="3" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J257" s="3" t="s">
-        <v>1118</v>
-      </c>
-      <c r="K257" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L257" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C258" s="2" t="s">
+      <c r="E258" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D258" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F258" s="2" t="s">
+      <c r="G258" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I258" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="G258" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I258" s="2" t="s">
-        <v>1123</v>
-      </c>
       <c r="J258" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="K258" s="2" t="s">
         <v>20</v>
@@ -14231,24 +14287,24 @@
         <v>191</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A259" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B259" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="C259" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="C259" s="3" t="s">
+      <c r="D259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F259" s="3" t="s">
         <v>1126</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E259" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>18</v>
@@ -14266,10 +14322,10 @@
         <v>20</v>
       </c>
       <c r="L259" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A260" s="2" t="s">
         <v>1128</v>
       </c>
@@ -14286,7 +14342,7 @@
         <v>16</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>18</v>
@@ -14304,10 +14360,10 @@
         <v>20</v>
       </c>
       <c r="L260" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A261" s="3" t="s">
         <v>1132</v>
       </c>
@@ -14318,13 +14374,13 @@
         <v>1134</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>325</v>
+        <v>15</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>18</v>
@@ -14345,7 +14401,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A262" s="2" t="s">
         <v>1136</v>
       </c>
@@ -14356,13 +14412,13 @@
         <v>1138</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>15</v>
+        <v>325</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>18</v>
@@ -14380,10 +14436,10 @@
         <v>20</v>
       </c>
       <c r="L262" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A263" s="3" t="s">
         <v>1140</v>
       </c>
@@ -14400,7 +14456,7 @@
         <v>16</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>18</v>
@@ -14418,10 +14474,10 @@
         <v>20</v>
       </c>
       <c r="L263" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A264" s="2" t="s">
         <v>1144</v>
       </c>
@@ -14438,7 +14494,7 @@
         <v>16</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>18</v>
@@ -14456,10 +14512,10 @@
         <v>20</v>
       </c>
       <c r="L264" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="265" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A265" s="3" t="s">
         <v>1148</v>
       </c>
@@ -14476,7 +14532,7 @@
         <v>16</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G265" s="3" t="s">
         <v>18</v>
@@ -14494,10 +14550,10 @@
         <v>20</v>
       </c>
       <c r="L265" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A266" s="2" t="s">
         <v>1152</v>
       </c>
@@ -14514,7 +14570,7 @@
         <v>16</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>18</v>
@@ -14532,10 +14588,10 @@
         <v>20</v>
       </c>
       <c r="L266" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="267" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A267" s="3" t="s">
         <v>1156</v>
       </c>
@@ -14570,10 +14626,10 @@
         <v>20</v>
       </c>
       <c r="L267" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A268" s="2" t="s">
         <v>1160</v>
       </c>
@@ -14584,13 +14640,13 @@
         <v>1162</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>325</v>
+        <v>15</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>326</v>
+        <v>42</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>18</v>
@@ -14608,10 +14664,10 @@
         <v>20</v>
       </c>
       <c r="L268" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="269" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A269" s="3" t="s">
         <v>1164</v>
       </c>
@@ -14622,13 +14678,13 @@
         <v>1166</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>15</v>
+        <v>325</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>18</v>
+        <v>326</v>
       </c>
       <c r="G269" s="3" t="s">
         <v>18</v>
@@ -14646,10 +14702,10 @@
         <v>20</v>
       </c>
       <c r="L269" s="3" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="270" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A270" s="2" t="s">
         <v>1168</v>
       </c>
@@ -14666,7 +14722,7 @@
         <v>16</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>18</v>
@@ -14684,10 +14740,10 @@
         <v>20</v>
       </c>
       <c r="L270" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="271" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A271" s="3" t="s">
         <v>1172</v>
       </c>
@@ -14704,7 +14760,7 @@
         <v>16</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="G271" s="3" t="s">
         <v>18</v>
@@ -14721,9 +14777,11 @@
       <c r="K271" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L271" s="3"/>
-    </row>
-    <row r="272" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L271" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A272" s="2" t="s">
         <v>1176</v>
       </c>
@@ -14740,7 +14798,7 @@
         <v>16</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>18</v>
@@ -14757,11 +14815,9 @@
       <c r="K272" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L272" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L272" s="2"/>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A273" s="3" t="s">
         <v>1180</v>
       </c>
@@ -14778,7 +14834,7 @@
         <v>16</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="G273" s="3" t="s">
         <v>18</v>
@@ -14796,10 +14852,10 @@
         <v>20</v>
       </c>
       <c r="L273" s="3" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="274" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A274" s="2" t="s">
         <v>1184</v>
       </c>
@@ -14816,7 +14872,7 @@
         <v>16</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>439</v>
+        <v>129</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>18</v>
@@ -14834,10 +14890,10 @@
         <v>20</v>
       </c>
       <c r="L274" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>951</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A275" s="3" t="s">
         <v>1188</v>
       </c>
@@ -14848,51 +14904,51 @@
         <v>1190</v>
       </c>
       <c r="D275" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I275" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="E275" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F275" s="3" t="s">
+      <c r="J275" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K275" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L275" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A276" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="G275" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H275" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I275" s="3" t="s">
+      <c r="B276" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="J275" s="3" t="s">
-        <v>1193</v>
-      </c>
-      <c r="K275" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="2" t="s">
+      <c r="C276" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="D276" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="E276" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>1196</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>18</v>
@@ -14910,10 +14966,10 @@
         <v>20</v>
       </c>
       <c r="L276" s="2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="277" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A277" s="3" t="s">
         <v>1198</v>
       </c>
@@ -14924,13 +14980,13 @@
         <v>1200</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>714</v>
+        <v>15</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>715</v>
+        <v>92</v>
       </c>
       <c r="G277" s="3" t="s">
         <v>18</v>
@@ -14948,10 +15004,10 @@
         <v>20</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>951</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A278" s="2" t="s">
         <v>1202</v>
       </c>
@@ -14962,13 +15018,13 @@
         <v>1204</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>15</v>
+        <v>714</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>129</v>
+        <v>715</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>18</v>
@@ -14986,10 +15042,10 @@
         <v>20</v>
       </c>
       <c r="L278" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="279" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A279" s="3" t="s">
         <v>1206</v>
       </c>
@@ -15000,72 +15056,72 @@
         <v>1208</v>
       </c>
       <c r="D279" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I279" s="3" t="s">
         <v>1209</v>
       </c>
-      <c r="E279" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F279" s="3" t="s">
+      <c r="J279" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K279" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L279" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A280" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="G279" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H279" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I279" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J279" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K279" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="L279" s="3" t="s">
+      <c r="G280" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H280" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I280" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J280" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K280" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L280" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="G280" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H280" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I280" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="J280" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="K280" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L280" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="281" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A281" s="3" t="s">
         <v>1215</v>
       </c>
@@ -15076,13 +15132,13 @@
         <v>1217</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>15</v>
+        <v>841</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>92</v>
+        <v>842</v>
       </c>
       <c r="G281" s="3" t="s">
         <v>18</v>
@@ -15091,17 +15147,19 @@
         <v>18</v>
       </c>
       <c r="I281" s="3" t="s">
-        <v>18</v>
+        <v>1218</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>18</v>
+        <v>1218</v>
       </c>
       <c r="K281" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="L281" s="3"/>
-    </row>
-    <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="L281" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A282" s="2" t="s">
         <v>1219</v>
       </c>
@@ -15112,51 +15170,49 @@
         <v>1221</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H282" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I282" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J282" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K282" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F282" s="2" t="s">
+      <c r="L282" s="2"/>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A283" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="G282" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H282" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I282" s="2" t="s">
+      <c r="B283" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="J282" s="2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="K282" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L282" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="283" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="3" t="s">
+      <c r="C283" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="D283" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="C283" s="3" t="s">
+      <c r="E283" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F283" s="3" t="s">
         <v>1227</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E283" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F283" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="G283" s="3" t="s">
         <v>18</v>
@@ -15174,10 +15230,10 @@
         <v>20</v>
       </c>
       <c r="L283" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="284" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A284" s="2" t="s">
         <v>1229</v>
       </c>
@@ -15188,13 +15244,13 @@
         <v>1231</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>841</v>
+        <v>15</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>842</v>
+        <v>179</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>18</v>
@@ -15212,10 +15268,10 @@
         <v>20</v>
       </c>
       <c r="L284" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="285" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A285" s="3" t="s">
         <v>1233</v>
       </c>
@@ -15226,13 +15282,13 @@
         <v>1235</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>15</v>
+        <v>841</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>18</v>
+        <v>842</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>18</v>
@@ -15250,10 +15306,10 @@
         <v>20</v>
       </c>
       <c r="L285" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A286" s="2" t="s">
         <v>1237</v>
       </c>
@@ -15270,7 +15326,7 @@
         <v>16</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>18</v>
@@ -15288,10 +15344,10 @@
         <v>20</v>
       </c>
       <c r="L286" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A287" s="3" t="s">
         <v>1241</v>
       </c>
@@ -15317,95 +15373,95 @@
         <v>18</v>
       </c>
       <c r="I287" s="3" t="s">
-        <v>18</v>
+        <v>1244</v>
       </c>
       <c r="J287" s="3" t="s">
-        <v>18</v>
+        <v>1244</v>
       </c>
       <c r="K287" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L287" s="3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A288" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H288" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I288" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J288" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K288" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L288" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D288" s="2" t="s">
+    <row customHeight="1" ht="15">
+      <c r="A289" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D289" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F288" s="2" t="s">
+      <c r="E289" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F289" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G288" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I288" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J288" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K288" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L288" s="2" t="s">
+      <c r="G289" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J289" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K289" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L289" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="3" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E289" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G289" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H289" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I289" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="J289" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="K289" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A290" s="2" t="s">
         <v>1251</v>
       </c>
@@ -15416,51 +15472,51 @@
         <v>1253</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H290" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I290" s="2" t="s">
         <v>1254</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F290" s="2" t="s">
+      <c r="J290" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="K290" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L290" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A291" s="3" t="s">
         <v>1255</v>
       </c>
-      <c r="G290" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H290" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I290" s="2" t="s">
+      <c r="B291" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="J290" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="K290" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L290" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="291" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A291" s="3" t="s">
+      <c r="C291" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="B291" s="3" t="s">
+      <c r="D291" s="3" t="s">
         <v>1258</v>
       </c>
-      <c r="C291" s="3" t="s">
+      <c r="E291" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291" s="3" t="s">
         <v>1259</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F291" s="3" t="s">
-        <v>664</v>
       </c>
       <c r="G291" s="3" t="s">
         <v>18</v>
@@ -15478,10 +15534,10 @@
         <v>20</v>
       </c>
       <c r="L291" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A292" s="2" t="s">
         <v>1261</v>
       </c>
@@ -15498,28 +15554,28 @@
         <v>16</v>
       </c>
       <c r="F292" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H292" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I292" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="G292" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I292" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="J292" s="2" t="s">
-        <v>18</v>
+        <v>1264</v>
       </c>
       <c r="K292" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L292" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A293" s="3" t="s">
         <v>1265</v>
       </c>
@@ -15536,7 +15592,7 @@
         <v>16</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>664</v>
+        <v>1268</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>18</v>
@@ -15545,19 +15601,19 @@
         <v>18</v>
       </c>
       <c r="I293" s="3" t="s">
-        <v>1268</v>
+        <v>18</v>
       </c>
       <c r="J293" s="3" t="s">
-        <v>1268</v>
+        <v>18</v>
       </c>
       <c r="K293" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L293" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="294" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A294" s="2" t="s">
         <v>1269</v>
       </c>
@@ -15592,10 +15648,10 @@
         <v>20</v>
       </c>
       <c r="L294" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="295" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A295" s="3" t="s">
         <v>1273</v>
       </c>
@@ -15612,7 +15668,7 @@
         <v>16</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>18</v>
+        <v>664</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>18</v>
@@ -15630,10 +15686,10 @@
         <v>20</v>
       </c>
       <c r="L295" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="296" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A296" s="2" t="s">
         <v>1277</v>
       </c>
@@ -15650,7 +15706,7 @@
         <v>16</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1122</v>
+        <v>18</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>18</v>
@@ -15668,10 +15724,10 @@
         <v>20</v>
       </c>
       <c r="L296" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="297" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A297" s="3" t="s">
         <v>1281</v>
       </c>
@@ -15688,121 +15744,121 @@
         <v>16</v>
       </c>
       <c r="F297" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J297" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="K297" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L297" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A298" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G297" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H297" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I297" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J297" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K297" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L297" s="3" t="s">
+      <c r="G298" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I298" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J298" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K298" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L298" s="2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A298" s="2" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I298" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J298" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K298" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L298" s="2" t="s">
+    <row customHeight="1" ht="15">
+      <c r="A299" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H299" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J299" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K299" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L299" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="3" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B299" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C299" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D299" s="3" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F299" s="3" t="s">
+    <row customHeight="1" ht="15">
+      <c r="A300" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F300" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="G299" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H299" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I299" s="3" t="s">
-        <v>1290</v>
-      </c>
-      <c r="J299" s="3" t="s">
-        <v>1290</v>
-      </c>
-      <c r="K299" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L299" s="3" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A300" s="2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>18</v>
@@ -15820,10 +15876,10 @@
         <v>20</v>
       </c>
       <c r="L300" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>951</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A301" s="3" t="s">
         <v>1295</v>
       </c>
@@ -15834,13 +15890,13 @@
         <v>1297</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="G301" s="3" t="s">
         <v>18</v>
@@ -15858,10 +15914,10 @@
         <v>20</v>
       </c>
       <c r="L301" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A302" s="2" t="s">
         <v>1299</v>
       </c>
@@ -15872,13 +15928,13 @@
         <v>1301</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>841</v>
+        <v>188</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>842</v>
+        <v>189</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>18</v>
@@ -15887,7 +15943,7 @@
         <v>18</v>
       </c>
       <c r="I302" s="2" t="s">
-        <v>18</v>
+        <v>1302</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>1302</v>
@@ -15896,10 +15952,10 @@
         <v>20</v>
       </c>
       <c r="L302" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A303" s="3" t="s">
         <v>1303</v>
       </c>
@@ -15910,13 +15966,13 @@
         <v>1305</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>15</v>
+        <v>841</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>1264</v>
+        <v>842</v>
       </c>
       <c r="G303" s="3" t="s">
         <v>18</v>
@@ -15925,7 +15981,7 @@
         <v>18</v>
       </c>
       <c r="I303" s="3" t="s">
-        <v>1306</v>
+        <v>18</v>
       </c>
       <c r="J303" s="3" t="s">
         <v>1306</v>
@@ -15934,10 +15990,10 @@
         <v>20</v>
       </c>
       <c r="L303" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A304" s="2" t="s">
         <v>1307</v>
       </c>
@@ -15954,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>461</v>
+        <v>1268</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>18</v>
@@ -15972,10 +16028,10 @@
         <v>20</v>
       </c>
       <c r="L304" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A305" s="3" t="s">
         <v>1311</v>
       </c>
@@ -15992,7 +16048,7 @@
         <v>16</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="G305" s="3" t="s">
         <v>18</v>
@@ -16001,7 +16057,7 @@
         <v>18</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>18</v>
+        <v>1314</v>
       </c>
       <c r="J305" s="3" t="s">
         <v>18</v>
@@ -16010,56 +16066,56 @@
         <v>406</v>
       </c>
       <c r="L305" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A306" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G306" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I306" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J306" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K306" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L306" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A306" s="2" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G306" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H306" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I306" s="2" t="s">
-        <v>1317</v>
-      </c>
-      <c r="J306" s="2" t="s">
-        <v>1317</v>
-      </c>
-      <c r="K306" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L306" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="15">
       <c r="A307" s="3" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>15</v>
@@ -16068,7 +16124,7 @@
         <v>16</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G307" s="3" t="s">
         <v>18</v>
@@ -16077,19 +16133,19 @@
         <v>18</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>1321</v>
+        <v>18</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>1321</v>
+        <v>18</v>
       </c>
       <c r="K307" s="3" t="s">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="L307" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A308" s="2" t="s">
         <v>1322</v>
       </c>
@@ -16124,10 +16180,10 @@
         <v>20</v>
       </c>
       <c r="L308" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
       <c r="A309" s="3" t="s">
         <v>1326</v>
       </c>
@@ -16138,13 +16194,13 @@
         <v>1328</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>18</v>
@@ -16156,17 +16212,282 @@
         <v>1329</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>18</v>
+        <v>1329</v>
       </c>
       <c r="K309" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L309" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A310" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F310" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G310" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H310" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I310" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="J310" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K310" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L310" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A311" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H311" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J311" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K311" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L311" s="3" t="s">
         <v>633</v>
       </c>
     </row>
+    <row customHeight="1" ht="15">
+      <c r="A312" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L312" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A313" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J313" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="K313" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L313" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A314" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I314" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="J314" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K314" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L314" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A315" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K315" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L315" s="3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A316" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K316" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L316" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup pageOrder="overThenDown" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
